--- a/data/date_landmark.xlsx
+++ b/data/date_landmark.xlsx
@@ -250,7 +250,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -264,6 +264,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -509,7 +513,7 @@
         <v>2011</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>40435</v>
+        <v>40429</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>40506</v>
@@ -537,8 +541,8 @@
       <c r="C3" s="2" t="n">
         <v>2011</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>40429</v>
+      <c r="D3" s="4" t="n">
+        <v>40435</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>40505</v>
@@ -856,7 +860,7 @@
       <c r="C14" s="2" t="n">
         <v>2015</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>41891</v>
       </c>
       <c r="E14" s="3" t="n">
@@ -886,7 +890,7 @@
         <v>2015</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>41909</v>
+        <v>41892</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>41973</v>
@@ -915,13 +919,13 @@
         <v>2015</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>41910</v>
+        <v>41884</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>41973</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>42070</v>
+        <v>42071</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>42107</v>
@@ -944,7 +948,7 @@
         <v>2015</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>41911</v>
+        <v>41887</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>41972</v>
